--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7703" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7704" uniqueCount="850">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t>Morphologie des Primärtumors nach ICD-O-3 nach 6.3 oBDS</t>
+  </si>
+  <si>
+    <t>An der Diagnose können mehrere Morphologie-Angaben stehen (0..*) — etwa bei gemischter Histologie oder Re-Klassifikation im Krankheitsverlauf. Befundbezogen wird jede Morphologie zusätzlich als Histologie-Observation (mii-pr-onko-histologie-icdo3) dokumentiert: dort genau eine Morphologie je Befund, mit Specimen- und Datumsbezug.</t>
   </si>
   <si>
     <t>Condition.extension:morphology-behavior-icdo3.id</t>
@@ -5161,7 +5164,9 @@
       <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -5236,10 +5241,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5345,10 +5350,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5454,10 +5459,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5483,13 +5488,13 @@
         <v>128</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5497,7 +5502,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -5539,7 +5544,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -5565,10 +5570,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5591,13 +5596,13 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5624,11 +5629,11 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -5646,7 +5651,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -5672,10 +5677,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5781,10 +5786,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5892,10 +5897,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5921,16 +5926,16 @@
         <v>140</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -5979,7 +5984,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -6005,10 +6010,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6114,10 +6119,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6225,10 +6230,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6254,23 +6259,23 @@
         <v>128</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>76</v>
@@ -6312,7 +6317,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -6338,10 +6343,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6367,13 +6372,13 @@
         <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6423,7 +6428,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -6441,7 +6446,7 @@
         <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>76</v>
@@ -6449,10 +6454,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6478,14 +6483,14 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -6534,7 +6539,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -6552,7 +6557,7 @@
         <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -6560,10 +6565,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6589,14 +6594,14 @@
         <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -6645,7 +6650,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -6671,10 +6676,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6697,19 +6702,19 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -6758,7 +6763,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6784,10 +6789,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6813,16 +6818,16 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -6871,7 +6876,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6889,7 +6894,7 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -6897,13 +6902,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>184</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
@@ -6925,13 +6930,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7008,10 +7013,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7117,10 +7122,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7226,10 +7231,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7255,13 +7260,13 @@
         <v>128</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7269,7 +7274,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>76</v>
@@ -7311,7 +7316,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>86</v>
@@ -7337,10 +7342,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7363,13 +7368,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7399,16 +7404,16 @@
         <v>152</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7418,7 +7423,7 @@
         <v>113</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -7444,13 +7449,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>76</v>
@@ -7472,13 +7477,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7529,7 +7534,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -7547,7 +7552,7 @@
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -7555,13 +7560,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>184</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>76</v>
@@ -7583,16 +7588,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7668,10 +7673,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7777,10 +7782,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7886,10 +7891,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7915,13 +7920,13 @@
         <v>128</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7929,7 +7934,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>76</v>
@@ -7971,7 +7976,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>86</v>
@@ -7997,10 +8002,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8023,13 +8028,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8059,16 +8064,16 @@
         <v>152</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8078,7 +8083,7 @@
         <v>113</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -8104,13 +8109,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>76</v>
@@ -8132,13 +8137,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8189,7 +8194,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -8215,13 +8220,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>76</v>
@@ -8243,13 +8248,13 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8326,10 +8331,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8355,16 +8360,16 @@
         <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -8413,7 +8418,7 @@
         <v>113</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -8439,10 +8444,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8465,19 +8470,19 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -8526,7 +8531,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -8552,10 +8557,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8661,10 +8666,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8772,10 +8777,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8801,16 +8806,16 @@
         <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -8835,13 +8840,13 @@
         <v>76</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>76</v>
@@ -8859,7 +8864,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8885,10 +8890,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8911,19 +8916,19 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -8951,10 +8956,10 @@
         <v>144</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>76</v>
@@ -8972,7 +8977,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8998,10 +9003,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9027,16 +9032,16 @@
         <v>128</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -9049,7 +9054,7 @@
         <v>76</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>76</v>
@@ -9085,7 +9090,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -9111,10 +9116,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9140,13 +9145,13 @@
         <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9160,7 +9165,7 @@
         <v>76</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>76</v>
@@ -9196,7 +9201,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -9222,10 +9227,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9248,13 +9253,13 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9305,7 +9310,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -9331,10 +9336,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9357,16 +9362,16 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9416,7 +9421,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -9442,10 +9447,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9468,16 +9473,16 @@
         <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9503,13 +9508,13 @@
         <v>76</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -9527,7 +9532,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -9536,7 +9541,7 @@
         <v>86</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
@@ -9548,15 +9553,15 @@
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9579,16 +9584,16 @@
         <v>87</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9614,13 +9619,13 @@
         <v>76</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -9638,7 +9643,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9647,7 +9652,7 @@
         <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -9664,10 +9669,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9773,10 +9778,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9884,10 +9889,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9913,16 +9918,16 @@
         <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -9959,7 +9964,7 @@
         <v>76</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
@@ -9969,7 +9974,7 @@
         <v>113</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9995,13 +10000,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>76</v>
@@ -10026,16 +10031,16 @@
         <v>140</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -10045,7 +10050,7 @@
         <v>76</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>76</v>
@@ -10060,11 +10065,11 @@
         <v>76</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>76</v>
@@ -10082,7 +10087,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -10108,13 +10113,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>76</v>
@@ -10139,16 +10144,16 @@
         <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -10158,7 +10163,7 @@
         <v>76</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>76</v>
@@ -10173,11 +10178,11 @@
         <v>76</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>76</v>
@@ -10195,7 +10200,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -10221,10 +10226,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10330,10 +10335,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10441,10 +10446,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10470,16 +10475,16 @@
         <v>128</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -10528,7 +10533,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -10554,10 +10559,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10583,13 +10588,13 @@
         <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10639,7 +10644,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10665,10 +10670,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10694,14 +10699,14 @@
         <v>162</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -10750,7 +10755,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10768,7 +10773,7 @@
         <v>76</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>76</v>
@@ -10776,10 +10781,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10805,14 +10810,14 @@
         <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>76</v>
@@ -10861,7 +10866,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10887,10 +10892,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10913,19 +10918,19 @@
         <v>87</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -10974,7 +10979,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -11000,10 +11005,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11029,16 +11034,16 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -11087,7 +11092,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -11113,10 +11118,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11139,16 +11144,16 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11177,10 +11182,10 @@
         <v>144</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>76</v>
@@ -11198,7 +11203,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -11224,10 +11229,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11250,16 +11255,16 @@
         <v>76</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11288,10 +11293,10 @@
         <v>166</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -11309,7 +11314,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -11335,14 +11340,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11361,19 +11366,19 @@
         <v>87</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>63</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -11401,10 +11406,10 @@
         <v>152</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>76</v>
@@ -11422,7 +11427,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -11448,10 +11453,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11557,10 +11562,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11668,10 +11673,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11697,16 +11702,16 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -11743,7 +11748,7 @@
         <v>76</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC79" s="2"/>
       <c r="AD79" t="s" s="2">
@@ -11753,7 +11758,7 @@
         <v>113</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11774,18 +11779,18 @@
         <v>76</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>76</v>
@@ -11807,19 +11812,19 @@
         <v>87</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -11829,7 +11834,7 @@
         <v>76</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>76</v>
@@ -11844,11 +11849,11 @@
         <v>76</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>76</v>
@@ -11866,7 +11871,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11878,7 +11883,7 @@
         <v>98</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>76</v>
@@ -11887,15 +11892,15 @@
         <v>76</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12001,10 +12006,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12112,13 +12117,13 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="B83" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="C83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>106</v>
@@ -12140,13 +12145,13 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>110</v>
@@ -12225,13 +12230,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>106</v>
@@ -12253,13 +12258,13 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>110</v>
@@ -12338,13 +12343,13 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>106</v>
@@ -12366,13 +12371,13 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>110</v>
@@ -12451,10 +12456,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12480,23 +12485,23 @@
         <v>128</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>76</v>
@@ -12538,7 +12543,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12564,10 +12569,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12593,13 +12598,13 @@
         <v>101</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12649,7 +12654,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12667,7 +12672,7 @@
         <v>76</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>76</v>
@@ -12675,10 +12680,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12704,16 +12709,16 @@
         <v>162</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>76</v>
@@ -12726,7 +12731,7 @@
         <v>76</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>76</v>
@@ -12762,7 +12767,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12774,24 +12779,24 @@
         <v>98</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12817,16 +12822,16 @@
         <v>101</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>76</v>
@@ -12875,7 +12880,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12901,10 +12906,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12927,19 +12932,19 @@
         <v>87</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>76</v>
@@ -12988,7 +12993,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -13014,13 +13019,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>76</v>
@@ -13042,19 +13047,19 @@
         <v>87</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>76</v>
@@ -13064,7 +13069,7 @@
         <v>76</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>76</v>
@@ -13079,11 +13084,11 @@
         <v>76</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>76</v>
@@ -13101,7 +13106,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -13122,15 +13127,15 @@
         <v>76</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13236,10 +13241,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13347,10 +13352,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13376,23 +13381,23 @@
         <v>128</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>76</v>
@@ -13434,7 +13439,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -13460,10 +13465,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13489,13 +13494,13 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13545,7 +13550,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13571,10 +13576,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13600,16 +13605,16 @@
         <v>162</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
@@ -13658,7 +13663,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13679,15 +13684,15 @@
         <v>76</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13713,16 +13718,16 @@
         <v>101</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>76</v>
@@ -13771,7 +13776,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13797,10 +13802,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13823,19 +13828,19 @@
         <v>87</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>76</v>
@@ -13884,7 +13889,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13910,13 +13915,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>76</v>
@@ -13941,16 +13946,16 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
@@ -13960,7 +13965,7 @@
         <v>76</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>76</v>
@@ -13975,11 +13980,11 @@
         <v>76</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>76</v>
@@ -13997,7 +14002,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -14018,15 +14023,15 @@
         <v>76</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14132,10 +14137,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14243,10 +14248,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14272,16 +14277,16 @@
         <v>128</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -14330,7 +14335,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -14356,10 +14361,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14385,13 +14390,13 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14441,7 +14446,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -14467,10 +14472,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14496,16 +14501,16 @@
         <v>162</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>76</v>
@@ -14554,7 +14559,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -14575,15 +14580,15 @@
         <v>76</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14609,16 +14614,16 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>76</v>
@@ -14667,7 +14672,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14693,10 +14698,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14719,19 +14724,19 @@
         <v>87</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>76</v>
@@ -14780,7 +14785,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14806,13 +14811,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>76</v>
@@ -14837,16 +14842,16 @@
         <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>76</v>
@@ -14856,7 +14861,7 @@
         <v>76</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>76</v>
@@ -14871,11 +14876,11 @@
         <v>76</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>76</v>
@@ -14893,7 +14898,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14914,15 +14919,15 @@
         <v>76</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15028,10 +15033,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15139,10 +15144,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15168,16 +15173,16 @@
         <v>128</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>76</v>
@@ -15226,7 +15231,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -15252,10 +15257,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15281,13 +15286,13 @@
         <v>101</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15337,7 +15342,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -15363,10 +15368,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15392,16 +15397,16 @@
         <v>162</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -15450,7 +15455,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -15471,15 +15476,15 @@
         <v>76</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15505,16 +15510,16 @@
         <v>101</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -15563,7 +15568,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -15589,10 +15594,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15615,19 +15620,19 @@
         <v>87</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -15676,7 +15681,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15702,10 +15707,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15731,16 +15736,16 @@
         <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
@@ -15789,7 +15794,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15807,18 +15812,18 @@
         <v>76</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15841,16 +15846,16 @@
         <v>87</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15879,10 +15884,10 @@
         <v>152</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>76</v>
@@ -15900,7 +15905,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15921,15 +15926,15 @@
         <v>76</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16035,10 +16040,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16146,10 +16151,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16175,16 +16180,16 @@
         <v>140</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
@@ -16221,7 +16226,7 @@
         <v>76</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AC119" s="2"/>
       <c r="AD119" t="s" s="2">
@@ -16231,7 +16236,7 @@
         <v>113</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -16257,13 +16262,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>76</v>
@@ -16288,16 +16293,16 @@
         <v>140</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>76</v>
@@ -16322,11 +16327,11 @@
         <v>76</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>76</v>
@@ -16344,7 +16349,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -16370,10 +16375,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16479,10 +16484,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16590,10 +16595,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16619,16 +16624,16 @@
         <v>128</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>76</v>
@@ -16638,7 +16643,7 @@
         <v>76</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>76</v>
@@ -16677,7 +16682,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -16703,10 +16708,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16732,13 +16737,13 @@
         <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16788,7 +16793,7 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -16814,10 +16819,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16843,16 +16848,16 @@
         <v>162</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>76</v>
@@ -16901,7 +16906,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16927,10 +16932,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16956,16 +16961,16 @@
         <v>101</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
@@ -17014,7 +17019,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -17040,10 +17045,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17066,19 +17071,19 @@
         <v>87</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>76</v>
@@ -17127,7 +17132,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -17153,13 +17158,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>76</v>
@@ -17184,16 +17189,16 @@
         <v>140</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>76</v>
@@ -17218,11 +17223,11 @@
         <v>76</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>76</v>
@@ -17240,7 +17245,7 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -17266,10 +17271,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17375,10 +17380,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17486,10 +17491,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17515,16 +17520,16 @@
         <v>128</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -17534,7 +17539,7 @@
         <v>76</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>76</v>
@@ -17573,7 +17578,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
@@ -17599,10 +17604,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17628,13 +17633,13 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17684,7 +17689,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -17710,10 +17715,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17739,14 +17744,14 @@
         <v>162</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
@@ -17795,7 +17800,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -17813,7 +17818,7 @@
         <v>76</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>76</v>
@@ -17821,10 +17826,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17850,14 +17855,14 @@
         <v>101</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
@@ -17906,7 +17911,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -17932,10 +17937,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17958,19 +17963,19 @@
         <v>87</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -18019,7 +18024,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -18045,13 +18050,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>76</v>
@@ -18076,16 +18081,16 @@
         <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
@@ -18110,11 +18115,11 @@
         <v>76</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>76</v>
@@ -18132,7 +18137,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -18158,10 +18163,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18267,10 +18272,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18378,10 +18383,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18407,16 +18412,16 @@
         <v>128</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>76</v>
@@ -18426,7 +18431,7 @@
         <v>76</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>76</v>
@@ -18465,7 +18470,7 @@
         <v>76</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
@@ -18491,10 +18496,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18520,13 +18525,13 @@
         <v>101</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18576,7 +18581,7 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
@@ -18594,7 +18599,7 @@
         <v>76</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>76</v>
@@ -18602,10 +18607,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18631,14 +18636,14 @@
         <v>162</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>76</v>
@@ -18687,7 +18692,7 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
@@ -18705,7 +18710,7 @@
         <v>76</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>76</v>
@@ -18713,10 +18718,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18742,14 +18747,14 @@
         <v>101</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>76</v>
@@ -18798,7 +18803,7 @@
         <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>77</v>
@@ -18824,10 +18829,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18850,19 +18855,19 @@
         <v>87</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>76</v>
@@ -18911,7 +18916,7 @@
         <v>76</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>77</v>
@@ -18937,10 +18942,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18966,16 +18971,16 @@
         <v>101</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>76</v>
@@ -19024,7 +19029,7 @@
         <v>76</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>77</v>
@@ -19050,14 +19055,14 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19076,19 +19081,19 @@
         <v>87</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>76</v>
@@ -19137,7 +19142,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>86</v>
@@ -19149,7 +19154,7 @@
         <v>98</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>76</v>
@@ -19163,10 +19168,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19189,16 +19194,16 @@
         <v>87</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19248,7 +19253,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -19260,7 +19265,7 @@
         <v>98</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>76</v>
@@ -19274,10 +19279,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19300,16 +19305,16 @@
         <v>87</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19347,7 +19352,7 @@
         <v>76</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AC147" s="2"/>
       <c r="AD147" t="s" s="2">
@@ -19357,7 +19362,7 @@
         <v>113</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -19378,18 +19383,18 @@
         <v>76</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D148" t="s" s="2">
         <v>76</v>
@@ -19411,16 +19416,16 @@
         <v>87</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19470,7 +19475,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -19491,15 +19496,15 @@
         <v>76</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19605,10 +19610,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19716,10 +19721,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19742,16 +19747,16 @@
         <v>87</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19801,7 +19806,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>77</v>
@@ -19810,7 +19815,7 @@
         <v>86</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>99</v>
@@ -19822,15 +19827,15 @@
         <v>76</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19936,10 +19941,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20047,13 +20052,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="B154" t="s" s="2">
-        <v>639</v>
-      </c>
       <c r="C154" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>106</v>
@@ -20075,13 +20080,13 @@
         <v>76</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>110</v>
@@ -20160,10 +20165,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20269,10 +20274,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20380,10 +20385,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20409,13 +20414,13 @@
         <v>128</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20423,7 +20428,7 @@
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>76</v>
@@ -20465,7 +20470,7 @@
         <v>76</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>86</v>
@@ -20491,10 +20496,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20517,13 +20522,13 @@
         <v>76</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -20574,7 +20579,7 @@
         <v>76</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>77</v>
@@ -20595,15 +20600,15 @@
         <v>76</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20709,10 +20714,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20820,10 +20825,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20849,16 +20854,16 @@
         <v>140</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>76</v>
@@ -20883,13 +20888,13 @@
         <v>76</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>76</v>
@@ -20907,7 +20912,7 @@
         <v>76</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>77</v>
@@ -20933,10 +20938,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21042,10 +21047,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21153,10 +21158,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21182,16 +21187,16 @@
         <v>128</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>76</v>
@@ -21240,7 +21245,7 @@
         <v>76</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>77</v>
@@ -21266,10 +21271,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21295,13 +21300,13 @@
         <v>101</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -21351,7 +21356,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>77</v>
@@ -21377,10 +21382,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21406,16 +21411,16 @@
         <v>162</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>76</v>
@@ -21464,7 +21469,7 @@
         <v>76</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
@@ -21490,10 +21495,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21519,16 +21524,16 @@
         <v>101</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>76</v>
@@ -21577,7 +21582,7 @@
         <v>76</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>77</v>
@@ -21603,10 +21608,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21629,19 +21634,19 @@
         <v>87</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>76</v>
@@ -21690,7 +21695,7 @@
         <v>76</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>77</v>
@@ -21716,10 +21721,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21745,16 +21750,16 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>76</v>
@@ -21803,7 +21808,7 @@
         <v>76</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>77</v>
@@ -21829,10 +21834,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21855,13 +21860,13 @@
         <v>76</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -21912,7 +21917,7 @@
         <v>76</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>77</v>
@@ -21938,10 +21943,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21964,23 +21969,23 @@
         <v>87</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q171" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="R171" t="s" s="2">
         <v>76</v>
@@ -22025,7 +22030,7 @@
         <v>76</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>77</v>
@@ -22034,7 +22039,7 @@
         <v>86</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>99</v>
@@ -22046,15 +22051,15 @@
         <v>76</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22160,10 +22165,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22271,13 +22276,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="B174" t="s" s="2">
-        <v>692</v>
-      </c>
       <c r="C174" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>106</v>
@@ -22299,13 +22304,13 @@
         <v>76</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>110</v>
@@ -22384,10 +22389,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22493,10 +22498,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22604,10 +22609,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22633,13 +22638,13 @@
         <v>128</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -22647,7 +22652,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>76</v>
@@ -22689,7 +22694,7 @@
         <v>76</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>86</v>
@@ -22715,10 +22720,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22741,13 +22746,13 @@
         <v>76</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -22798,7 +22803,7 @@
         <v>76</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>77</v>
@@ -22819,15 +22824,15 @@
         <v>76</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22933,10 +22938,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23044,10 +23049,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23073,16 +23078,16 @@
         <v>140</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>76</v>
@@ -23107,13 +23112,13 @@
         <v>76</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>76</v>
@@ -23131,7 +23136,7 @@
         <v>76</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>77</v>
@@ -23157,10 +23162,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23266,10 +23271,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23377,10 +23382,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23406,16 +23411,16 @@
         <v>128</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>76</v>
@@ -23464,7 +23469,7 @@
         <v>76</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>77</v>
@@ -23490,10 +23495,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23519,13 +23524,13 @@
         <v>101</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -23575,7 +23580,7 @@
         <v>76</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>77</v>
@@ -23601,10 +23606,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23630,16 +23635,16 @@
         <v>162</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>76</v>
@@ -23688,7 +23693,7 @@
         <v>76</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>77</v>
@@ -23714,10 +23719,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23743,16 +23748,16 @@
         <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>76</v>
@@ -23801,7 +23806,7 @@
         <v>76</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>77</v>
@@ -23827,10 +23832,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23853,19 +23858,19 @@
         <v>87</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>76</v>
@@ -23914,7 +23919,7 @@
         <v>76</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>77</v>
@@ -23940,10 +23945,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23969,16 +23974,16 @@
         <v>101</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>76</v>
@@ -24027,7 +24032,7 @@
         <v>76</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>77</v>
@@ -24053,10 +24058,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24079,13 +24084,13 @@
         <v>76</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -24136,7 +24141,7 @@
         <v>76</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>77</v>
@@ -24162,13 +24167,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>76</v>
@@ -24190,16 +24195,16 @@
         <v>87</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -24249,7 +24254,7 @@
         <v>76</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>77</v>
@@ -24275,13 +24280,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>76</v>
@@ -24303,16 +24308,16 @@
         <v>87</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -24362,7 +24367,7 @@
         <v>76</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
@@ -24388,10 +24393,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24497,10 +24502,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24608,13 +24613,13 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D195" t="s" s="2">
         <v>106</v>
@@ -24636,16 +24641,16 @@
         <v>76</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -24721,10 +24726,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24747,19 +24752,19 @@
         <v>87</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>76</v>
@@ -24808,7 +24813,7 @@
         <v>76</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>77</v>
@@ -24834,10 +24839,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24863,22 +24868,22 @@
         <v>162</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q197" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="R197" t="s" s="2">
         <v>76</v>
@@ -24899,13 +24904,13 @@
         <v>76</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>76</v>
@@ -24923,7 +24928,7 @@
         <v>76</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>77</v>
@@ -24949,10 +24954,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24978,16 +24983,16 @@
         <v>101</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>76</v>
@@ -25036,7 +25041,7 @@
         <v>76</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>77</v>
@@ -25062,10 +25067,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25091,16 +25096,16 @@
         <v>128</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>76</v>
@@ -25149,7 +25154,7 @@
         <v>76</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>77</v>
@@ -25158,7 +25163,7 @@
         <v>86</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AJ199" t="s" s="2">
         <v>99</v>
@@ -25175,10 +25180,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25204,16 +25209,16 @@
         <v>162</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>76</v>
@@ -25262,7 +25267,7 @@
         <v>76</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>77</v>
@@ -25288,10 +25293,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25314,16 +25319,16 @@
         <v>76</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -25373,7 +25378,7 @@
         <v>76</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>77</v>
@@ -25382,7 +25387,7 @@
         <v>86</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>99</v>
@@ -25399,10 +25404,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25425,13 +25430,13 @@
         <v>87</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -25482,7 +25487,7 @@
         <v>76</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>77</v>
@@ -25503,15 +25508,15 @@
         <v>76</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25534,16 +25539,16 @@
         <v>87</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -25593,7 +25598,7 @@
         <v>76</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>77</v>
@@ -25605,7 +25610,7 @@
         <v>98</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>76</v>
@@ -25619,10 +25624,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25645,16 +25650,16 @@
         <v>87</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -25704,7 +25709,7 @@
         <v>76</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>77</v>
@@ -25716,7 +25721,7 @@
         <v>98</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>76</v>
@@ -25730,10 +25735,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25756,13 +25761,13 @@
         <v>76</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -25813,7 +25818,7 @@
         <v>76</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>77</v>
@@ -25825,7 +25830,7 @@
         <v>98</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AK205" t="s" s="2">
         <v>76</v>
@@ -25839,10 +25844,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25948,10 +25953,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -26059,14 +26064,14 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
@@ -26088,16 +26093,16 @@
         <v>107</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N208" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>76</v>
@@ -26146,7 +26151,7 @@
         <v>76</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>77</v>
@@ -26172,10 +26177,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -26198,16 +26203,16 @@
         <v>76</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -26236,10 +26241,10 @@
         <v>152</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>76</v>
@@ -26257,7 +26262,7 @@
         <v>76</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -26266,7 +26271,7 @@
         <v>86</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>99</v>
@@ -26283,10 +26288,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26309,16 +26314,16 @@
         <v>76</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -26368,7 +26373,7 @@
         <v>76</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -26377,10 +26382,10 @@
         <v>78</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>76</v>
@@ -26394,10 +26399,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -26420,16 +26425,16 @@
         <v>76</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -26458,10 +26463,10 @@
         <v>152</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>76</v>
@@ -26479,7 +26484,7 @@
         <v>76</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>77</v>
@@ -26505,10 +26510,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -26531,16 +26536,16 @@
         <v>76</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -26590,7 +26595,7 @@
         <v>76</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>77</v>
@@ -26602,7 +26607,7 @@
         <v>98</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>76</v>
@@ -26616,10 +26621,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26725,10 +26730,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26836,14 +26841,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -26865,16 +26870,16 @@
         <v>107</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N215" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>76</v>
@@ -26923,7 +26928,7 @@
         <v>76</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>77</v>
@@ -26949,10 +26954,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26975,16 +26980,16 @@
         <v>87</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -27013,10 +27018,10 @@
         <v>152</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>76</v>
@@ -27034,7 +27039,7 @@
         <v>76</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>77</v>
@@ -27043,7 +27048,7 @@
         <v>78</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>99</v>
@@ -27060,10 +27065,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -27086,16 +27091,16 @@
         <v>87</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
@@ -27145,7 +27150,7 @@
         <v>76</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>77</v>
@@ -27154,10 +27159,10 @@
         <v>78</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>76</v>
@@ -27171,10 +27176,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27197,16 +27202,16 @@
         <v>76</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
@@ -27256,7 +27261,7 @@
         <v>76</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>77</v>
@@ -27277,7 +27282,7 @@
         <v>76</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
